--- a/artfynd/A 22023-2026 artfynd.xlsx
+++ b/artfynd/A 22023-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135574699</v>
       </c>
       <c r="B2" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135574701</v>
       </c>
       <c r="B3" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135574703</v>
       </c>
       <c r="B4" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135574694</v>
       </c>
       <c r="B5" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135574705</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135574707</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>135574708</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>135574710</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>135574714</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>135574715</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>135574700</v>
       </c>
       <c r="B12" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>135574695</v>
       </c>
       <c r="B13" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>135574709</v>
       </c>
       <c r="B14" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22023-2026 artfynd.xlsx
+++ b/artfynd/A 22023-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135574699</v>
       </c>
       <c r="B2" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135574701</v>
       </c>
       <c r="B3" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135574703</v>
       </c>
       <c r="B4" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>135574695</v>
       </c>
       <c r="B13" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>135574709</v>
       </c>
       <c r="B14" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22023-2026 artfynd.xlsx
+++ b/artfynd/A 22023-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135574699</v>
       </c>
       <c r="B2" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135574701</v>
       </c>
       <c r="B3" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135574703</v>
       </c>
       <c r="B4" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>135574695</v>
       </c>
       <c r="B13" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>135574709</v>
       </c>
       <c r="B14" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
